--- a/files/data/Traits.xlsx
+++ b/files/data/Traits.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexandreETIENNE\Downloads\pERSO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/054f950197fbca64/Documents/Jeu/PavillonNoirLogiciel/LogicielPNGaming/files/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2AD58D5-8BDD-4C77-9363-2DBF5497C755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{B2AD58D5-8BDD-4C77-9363-2DBF5497C755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9881579-1E60-4DF7-9EE8-C42CE7D36A20}"/>
   <bookViews>
-    <workbookView xWindow="-1140" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{18E8458F-5FC7-40D3-B3A0-FCFA88649893}"/>
+    <workbookView xWindow="588" yWindow="13548" windowWidth="21600" windowHeight="11292" xr2:uid="{18E8458F-5FC7-40D3-B3A0-FCFA88649893}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
   <si>
     <t>Col</t>
   </si>
@@ -215,9 +204,6 @@
     <t>Espagnol</t>
   </si>
   <si>
-    <t>Interprète</t>
-  </si>
-  <si>
     <t>Néerlandais</t>
   </si>
   <si>
@@ -243,6 +229,18 @@
   </si>
   <si>
     <t>Artilleur</t>
+  </si>
+  <si>
+    <t>InterprèteAnglais</t>
+  </si>
+  <si>
+    <t>InterprèteEspagnol</t>
+  </si>
+  <si>
+    <t>InterprètePortuguais</t>
+  </si>
+  <si>
+    <t>InterprèteNeerlandais</t>
   </si>
 </sst>
 </file>
@@ -955,7 +953,7 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -966,73 +964,73 @@
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
         <v>63</v>
-      </c>
-      <c r="B36">
-        <v>2</v>
-      </c>
-      <c r="C36" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
         <v>65</v>
-      </c>
-      <c r="B37">
-        <v>2</v>
-      </c>
-      <c r="C37" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38" t="s">
         <v>67</v>
-      </c>
-      <c r="B38">
-        <v>2</v>
-      </c>
-      <c r="C38" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/files/data/Traits.xlsx
+++ b/files/data/Traits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/054f950197fbca64/Documents/Jeu/PavillonNoirLogiciel/LogicielPNGaming/files/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{B2AD58D5-8BDD-4C77-9363-2DBF5497C755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9881579-1E60-4DF7-9EE8-C42CE7D36A20}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{B2AD58D5-8BDD-4C77-9363-2DBF5497C755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B2B29DF-E1AA-43E2-81D9-104C1D2FA662}"/>
   <bookViews>
-    <workbookView xWindow="588" yWindow="13548" windowWidth="21600" windowHeight="11292" xr2:uid="{18E8458F-5FC7-40D3-B3A0-FCFA88649893}"/>
+    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{18E8458F-5FC7-40D3-B3A0-FCFA88649893}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="76">
   <si>
     <t>Col</t>
   </si>
@@ -241,6 +241,18 @@
   </si>
   <si>
     <t>InterprèteNeerlandais</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Navigateur</t>
+  </si>
+  <si>
+    <t>Hydrographie</t>
+  </si>
+  <si>
+    <t>Hydrographe</t>
   </si>
 </sst>
 </file>
@@ -612,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0530DE92-7D37-4C1A-BDF3-4A4B6A10D1E0}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1033,6 +1045,28 @@
         <v>67</v>
       </c>
     </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40">
+        <v>2</v>
+      </c>
+      <c r="C40" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/files/data/Traits.xlsx
+++ b/files/data/Traits.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/054f950197fbca64/Documents/Jeu/PavillonNoirLogiciel/LogicielPNGaming/files/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{B2AD58D5-8BDD-4C77-9363-2DBF5497C755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B2B29DF-E1AA-43E2-81D9-104C1D2FA662}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{B2AD58D5-8BDD-4C77-9363-2DBF5497C755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{917870AA-AC16-45F5-9A88-6E58BA674E59}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{18E8458F-5FC7-40D3-B3A0-FCFA88649893}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="84">
   <si>
     <t>Col</t>
   </si>
@@ -253,6 +256,30 @@
   </si>
   <si>
     <t>Hydrographe</t>
+  </si>
+  <si>
+    <t>Balistique</t>
+  </si>
+  <si>
+    <t>Balisticien</t>
+  </si>
+  <si>
+    <t>Cartographie</t>
+  </si>
+  <si>
+    <t>Cartographe</t>
+  </si>
+  <si>
+    <t>Géographie</t>
+  </si>
+  <si>
+    <t>Géographe</t>
+  </si>
+  <si>
+    <t>Herboristerie</t>
+  </si>
+  <si>
+    <t>Herboriste</t>
   </si>
 </sst>
 </file>
@@ -624,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0530DE92-7D37-4C1A-BDF3-4A4B6A10D1E0}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -640,139 +667,139 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -783,112 +810,112 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -904,170 +931,219 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>75</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{0530DE92-7D37-4C1A-BDF3-4A4B6A10D1E0}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C40">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>